--- a/excel-files/NAVOTAS/NAVOTAS I ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/NAVOTAS I ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CB3189F-9F1B-470D-A85C-A4D89BC16006}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05DF5CD4-2BCD-40B0-9118-E92A48F6B068}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -3711,17 +3711,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>112</v>
+      </c>
+      <c r="D11" s="1">
+        <v>135</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3814,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3884,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3904,7 +3912,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>91</v>
@@ -3916,7 +3924,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3944,7 +3952,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3972,7 +3980,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -4000,7 +4008,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -4016,7 +4024,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>91</v>
@@ -4028,7 +4036,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4056,7 +4064,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4094,17 +4102,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>91</v>
+      </c>
+      <c r="D29" s="1">
+        <v>146</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4122,7 +4138,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>79</v>
@@ -4134,7 +4150,7 @@
         <v>2025</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
@@ -4150,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4222,7 +4238,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4238,7 +4254,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>79</v>
@@ -4250,7 +4266,7 @@
         <v>2025</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
@@ -4278,7 +4294,7 @@
         <v>2025</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
@@ -4296,17 +4312,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>79</v>
+      </c>
+      <c r="D38" s="1">
+        <v>99</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4344,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4364,7 +4388,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4444,7 +4468,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4534,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4554,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4634,7 +4658,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4724,7 +4748,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4744,7 +4768,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4824,7 +4848,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4914,7 +4938,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4934,7 +4958,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -5014,7 +5038,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5104,7 +5128,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5124,7 +5148,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5204,7 +5228,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5456,8 +5480,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E91:E98 E21:E29 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5472,7 +5496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6047,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6116,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6262,7 +6286,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6469,24 +6493,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>112</v>
+      </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6494,29 +6520,36 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+        <v>896</v>
+      </c>
+      <c r="K17" s="5">
+        <f>115*8</f>
+        <v>920</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6524,14 +6557,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
@@ -6607,24 +6640,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C19" s="1">
+        <v>112</v>
+      </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6632,29 +6667,36 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="5"/>
+        <v>896</v>
+      </c>
+      <c r="K19" s="5">
+        <f>115*8</f>
+        <v>920</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6662,14 +6704,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
@@ -6681,7 +6723,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6828,7 +6870,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6966,39 +7008,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1">
+        <v>82</v>
+      </c>
       <c r="D25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="5"/>
+        <v>656</v>
+      </c>
+      <c r="E25" s="5">
+        <f>88*8</f>
+        <v>704</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H25" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" si="11"/>
@@ -7006,14 +7057,14 @@
       </c>
       <c r="P25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="13"/>
@@ -7021,14 +7072,14 @@
       </c>
       <c r="V25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="W25" s="5"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="15"/>
@@ -7040,7 +7091,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7247,7 +7298,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7311,39 +7362,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C30" s="1">
+        <v>82</v>
+      </c>
       <c r="D30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="5"/>
+        <v>656</v>
+      </c>
+      <c r="E30" s="5">
+        <f>88*8</f>
+        <v>704</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
         <v>0</v>
       </c>
       <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="O30" s="5">
         <f t="shared" si="11"/>
@@ -7351,14 +7411,14 @@
       </c>
       <c r="P30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" si="13"/>
@@ -7366,14 +7426,14 @@
       </c>
       <c r="V30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="W30" s="5"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="15"/>
@@ -7468,7 +7528,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7537,7 +7597,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7739,7 +7799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7813,7 +7873,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8015,24 +8075,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>91</v>
+      </c>
       <c r="D41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="3"/>
@@ -8040,14 +8102,14 @@
       </c>
       <c r="J41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="O41" s="5">
         <f t="shared" si="11"/>
@@ -8055,29 +8117,36 @@
       </c>
       <c r="P41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="5"/>
+        <v>728</v>
+      </c>
+      <c r="Q41" s="5">
+        <f>117*8</f>
+        <v>936</v>
+      </c>
+      <c r="R41" s="1">
+        <v>2025</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="T41" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="V41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="W41" s="5"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="15"/>
@@ -8098,24 +8167,26 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C43" s="1">
+        <v>79</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8123,14 +8194,21 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+        <v>632</v>
+      </c>
+      <c r="K43" s="5">
+        <f>73*8</f>
+        <v>584</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8138,14 +8216,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8153,26 +8231,26 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8236,24 +8314,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>79</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8261,14 +8341,21 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="5"/>
+        <v>632</v>
+      </c>
+      <c r="K45" s="5">
+        <f>73*8</f>
+        <v>584</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8276,14 +8363,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8291,14 +8378,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
@@ -8374,7 +8461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8448,7 +8535,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8738,7 +8825,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8807,7 +8894,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9083,7 +9170,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9373,7 +9460,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9442,7 +9529,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9718,7 +9805,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10008,7 +10095,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10077,7 +10164,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10353,7 +10440,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10643,7 +10730,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10712,7 +10799,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10988,7 +11075,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11278,7 +11365,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11347,7 +11434,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11623,7 +11710,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13460,191 +13547,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C2:C3 C14:C18 C23:C31 C33:C41 C44 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C20:C21 C46:C51" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 K14:L21 D23:F31 Q33:R41 D43:F51 K43:L51" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 Y5:Y12 G14:G21 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 S4:S110 M14:M110" name="SOURCE"/>
+    <protectedRange sqref="C19" name="Textbooks_1"/>
+    <protectedRange sqref="C43" name="Textbooks_2"/>
+    <protectedRange sqref="C45" name="Textbooks_3"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13657,10 +13567,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 R33:R41 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 X5:X12 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 L43:L51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S4:S110 Y14:Y110 G103:G110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13676,7 +13586,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14172,7 +14082,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14241,7 +14151,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14725,7 +14635,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14794,7 +14704,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -15140,7 +15050,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15347,7 +15257,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15416,7 +15326,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15555,7 +15465,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15624,7 +15534,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15900,7 +15810,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16315,7 +16225,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16384,7 +16294,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16660,7 +16570,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17075,7 +16985,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>97</v>
@@ -17135,12 +17045,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W55" s="5"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="5"/>
+      <c r="W55" s="5">
+        <v>140</v>
+      </c>
+      <c r="X55" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y55" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z55" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>636</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="7"/>
@@ -17152,7 +17068,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>97</v>
@@ -17212,12 +17128,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W56" s="5"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="5"/>
+      <c r="W56" s="5">
+        <v>100</v>
+      </c>
+      <c r="X56" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y56" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z56" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>676</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="7"/>
@@ -17289,12 +17211,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W57" s="5"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="5"/>
+      <c r="W57" s="5">
+        <v>180</v>
+      </c>
+      <c r="X57" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y57" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z57" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>596</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="7"/>
@@ -17366,12 +17294,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W58" s="5"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="5"/>
+      <c r="W58" s="5">
+        <v>40</v>
+      </c>
+      <c r="X58" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y58" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z58" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>736</v>
       </c>
       <c r="AA58" s="5">
         <f t="shared" si="7"/>
@@ -17443,12 +17377,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W59" s="5"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="5"/>
+      <c r="W59" s="5">
+        <v>140</v>
+      </c>
+      <c r="X59" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y59" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z59" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>636</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="7"/>
@@ -17460,7 +17400,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>97</v>
@@ -17520,12 +17460,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W60" s="5"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="5"/>
+      <c r="W60" s="5">
+        <v>160</v>
+      </c>
+      <c r="X60" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y60" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z60" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>616</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="7"/>
@@ -17597,12 +17543,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W61" s="5"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="5"/>
+      <c r="W61" s="5">
+        <v>60</v>
+      </c>
+      <c r="X61" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y61" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z61" s="5">
         <f>IF((V61-W61)&lt;0,0,(V61-W61))</f>
-        <v>776</v>
+        <v>716</v>
       </c>
       <c r="AA61" s="5">
         <f>IF((W61-V61)&lt;0,0,(W61-V61))</f>
@@ -17674,12 +17626,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W62" s="5"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="5"/>
+      <c r="W62" s="5">
+        <v>180</v>
+      </c>
+      <c r="X62" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y62" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z62" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>596</v>
       </c>
       <c r="AA62" s="5">
         <f t="shared" si="7"/>
@@ -17820,12 +17778,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W64" s="5"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="5"/>
+      <c r="W64" s="5">
+        <v>60</v>
+      </c>
+      <c r="X64" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y64" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z64" s="5">
         <f>IF((V64-W64)&lt;0,0,(V64-W64))</f>
-        <v>776</v>
+        <v>716</v>
       </c>
       <c r="AA64" s="5">
         <f>IF((W64-V64)&lt;0,0,(W64-V64))</f>
@@ -17897,12 +17861,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>776</v>
       </c>
-      <c r="W65" s="5"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="5"/>
+      <c r="W65" s="5">
+        <v>180</v>
+      </c>
+      <c r="X65" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y65" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z65" s="5">
         <f t="shared" si="6"/>
-        <v>776</v>
+        <v>596</v>
       </c>
       <c r="AA65" s="5">
         <f t="shared" si="7"/>
@@ -17915,7 +17885,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17984,7 +17954,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18260,7 +18230,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18675,7 +18645,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18744,7 +18714,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19020,7 +18990,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19435,7 +19405,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19504,7 +19474,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19780,7 +19750,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20120,7 +20090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20195,7 +20165,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20264,7 +20234,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20540,7 +20510,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22013,191 +21983,11 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N67:R77 N79:R89 N91:R101 N103:R113 N55:R65" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 S55:S65" name="SOURCE"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N67:R77 N79:R89 N91:R101 N103:R113 N55:R65 T55:X65" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 G55:G65 M55:M65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 S55:S65 Y55:Y65" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -22207,11 +21997,11 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 M115:M122 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 S55:S65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 S55:S65 M115:M122 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 F103:F113 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 R55:R65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X3:X10 X43:X53 X31:X41 X21:X29 X12:X19 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
